--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45057</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>45447</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45742</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>44648</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45456</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>45009</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>45912</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>45043</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45884</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>45638</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>44694</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44881</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>46281</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>46257</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44588</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>46000</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45394</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45587</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45734</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>44599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>45056</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>45450</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45440</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45958</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>46205</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45832</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>46230</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>46084</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44608</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>44897</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>45611</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>45252</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>45404</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45975</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45659</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>46167</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>46013</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>46010</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44665</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45513</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>46185</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>46094</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>46203</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>46090</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>45590</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44603</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>46070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>44524</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>44746</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>44774</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44831</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44818</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>45260</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>44831</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44864</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44462</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44461</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44461</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44504</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44608</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44551</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>44620</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44770</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44608</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44580</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>44826</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44862</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44620</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>44524</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44620</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>44524</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>44774</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>44490</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>44484</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45469</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>45601</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>45471</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45195</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45117</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45602</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45536</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45345</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45247</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44827</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>45481</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45615</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45189</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>45145</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45257</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>45511</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45446</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>45399</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45418</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>44919</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45128</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>45568</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>44475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44795</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44536</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>45187</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>45345</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44949</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>45251</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>45587</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>45602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>44950</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>45602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>45602</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>45609</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>45198</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>44776</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45630</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>45362</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45679</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45631</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>45436</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45600</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>45887</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>45467</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44978</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45190</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>45889</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45889</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>45889</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45889</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45069</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45393</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45394</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>45394</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45345</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45897</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45919</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45908</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45407</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>45582</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>44919</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>45915</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45614</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45649</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44701</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45916</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44991</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>46010</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>46023</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45102</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45929</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45929</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>46142</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>45348</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45181</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45019</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>46142</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>46142</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45099</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44998</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45537</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44722</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45938</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45938</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>45450</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45451</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>45943</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>44784</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45721</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45945</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>45946</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>45609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>46153</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44785</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45953</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45175</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45953</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45627</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45737</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>46153</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45232</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45964</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>44756</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45568</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45548</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45537</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44911</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45975</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45979</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45978</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45307</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45659</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>44899</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45982</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45755</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45982</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>44602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45986</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45989</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45988</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45259</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45989</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45988</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45988</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45993</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45351</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>46163</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45246</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45280</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45610</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>46167</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>46001</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>46001</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>46001</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>46164</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>46167</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45190</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>46001</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45615</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45568</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>46167</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>46002</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>46167</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>46167</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>46007</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46008</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>46008</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45183</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45737</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45280</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>44792</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45476</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45260</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>46171</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>46171</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>46171</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>46171</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44673</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>46041</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>46174</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>46174</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45602</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>46044</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45812</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>46176</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>46175</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45630</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>45469</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>46175</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45132</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>46055</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45614</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>46055</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>46057</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46057</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46056</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46177</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>46057</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>46177</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45429</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>45756</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>46010</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>46065</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>46181</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46181</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45513</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>46181</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45506</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>45247</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45293</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>46084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45236</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>46183</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>46185</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44806</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45447</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>46185</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>46188</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>46185</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45141</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45141</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45614</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>44788</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45348</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45348</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>46191</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>45009</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44887</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>46195</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45307</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>46197</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>46197</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>45587</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>46197</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44985</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45450</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>46198</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45351</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>46202</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46202</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>46202</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44494</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44608</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>46202</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45190</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>46132</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>46132</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>46132</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45406</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46132</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>46205</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44977</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>46205</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>46205</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>46203</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>46205</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>46205</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>46205</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45090</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45693</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>46246</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>46247</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>46205</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45642</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45189</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>46248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>46248</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>44911</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45224</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45512</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45539</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44557</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46255</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>46008</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>46254</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44916</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>46254</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>46254</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>46254</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45429</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46212</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>46254</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45076</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>46259</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45072</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45139</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>46190</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>44866</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45609</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>45436</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45168</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>46224</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>46264</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>46266</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>46267</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>46239</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45600</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45712</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45749</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>46225</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>46269</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>46248</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45881</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46270</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>46230</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>46230</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>46274</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>46275</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>46275</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>46275</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>46275</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>46279</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>46281</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>46281</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45790</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>45484</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46238</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45567</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45800</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45251</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45810</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45813</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45813</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>45813</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45825</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45831</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45834</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45838</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45846</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45846</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>45800</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45873</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45874</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45875</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45758</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45874</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45882</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45882</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45638</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45393</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>45393</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44642</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>44559</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>45250</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>45756</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45964</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>46135</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>46150</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>

--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45447</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>45057</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45742</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45607</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45009</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45456</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>44648</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45884</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45043</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45638</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44881</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>44694</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46257</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45394</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46000</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45440</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45897</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45587</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45056</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45450</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46084</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>46230</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44608</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45404</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>45513</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>46094</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>45975</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>46010</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>46013</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45611</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>45659</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>46167</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>46185</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>46203</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>46090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45252</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44608</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44665</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45590</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44603</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45756</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>46070</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>44774</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>44831</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>44818</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45260</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>44831</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>44864</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44504</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>44551</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44620</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>44770</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>44608</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>44826</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44862</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>44524</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44620</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44620</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44524</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44774</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44484</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45247</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45678</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45069</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45190</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44806</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45393</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45394</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45394</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>45450</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45407</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44784</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>45481</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45467</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>45484</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>45446</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44949</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44866</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45567</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>45512</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45539</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45447</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45506</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44494</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45476</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45887</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45548</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45889</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45614</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45436</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45800</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>46041</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>46044</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45897</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45429</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>45469</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45908</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>46056</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45348</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>46055</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>46055</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>46057</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>46057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>46057</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45915</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45915</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45916</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45919</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45251</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>46065</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45568</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45195</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>45929</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>45929</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45929</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45399</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45630</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>46084</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44914</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45938</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45938</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45587</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45568</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45943</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>44756</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>45945</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45946</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45236</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>45737</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45187</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45810</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>44673</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45712</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45953</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45953</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45351</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44998</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45964</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45614</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45813</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45813</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45076</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>45813</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>46132</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>46132</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>46132</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45978</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>46132</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45975</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45978</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>45679</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45979</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45982</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45232</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45982</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45986</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45600</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45128</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45988</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45988</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45630</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45989</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45988</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45989</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45993</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45072</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>46001</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46001</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>46002</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>46001</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46001</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>46008</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>46008</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>44978</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45749</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46007</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>44916</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44827</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45582</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44788</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45649</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45568</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45825</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>46023</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45257</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>46142</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45141</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>46010</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>44536</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>46142</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45919</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45280</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45537</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>46142</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44475</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45831</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44911</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>46153</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45614</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45737</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>46153</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45834</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45838</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>44602</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45345</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45351</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>44919</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45846</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45846</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>46164</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>46167</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>46167</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>46167</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>46167</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>46167</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         <v>44887</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45117</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>45601</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>46171</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>46171</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>46171</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>46171</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45800</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44557</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45513</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>46175</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45469</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>46175</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>46174</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>45602</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45812</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>46174</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>46177</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>46010</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>46177</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45537</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>46176</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44977</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>46181</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>46181</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>46181</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>46183</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45758</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>46185</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46185</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45602</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>46185</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>46188</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>45874</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>46191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45874</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>45418</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45642</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45875</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>46195</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>46197</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>46197</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45189</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>46198</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45882</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45471</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>46202</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45882</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>46202</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>46202</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>46202</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>46203</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45190</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>46205</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>46205</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>46205</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>46205</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>46205</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>46205</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>46205</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45345</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45609</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45610</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45587</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45090</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45429</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>46008</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45198</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>46254</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>46255</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45190</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>46212</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>46254</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>46254</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>46254</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45721</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45260</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>46254</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>46259</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45511</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45181</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>45145</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>44701</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>46190</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45307</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>44722</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45307</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>46264</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>45756</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45247</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>46266</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>46267</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45183</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45362</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>46224</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>46225</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45755</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45139</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45293</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>46270</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>45259</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>46239</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>46269</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45881</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45450</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45451</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>46248</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
         <v>45436</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>46274</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45251</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>46230</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46230</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>46275</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>46275</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45348</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45348</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>46275</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45345</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>46275</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45693</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45141</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>46279</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>45099</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>46281</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>46238</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>46281</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45536</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>46286</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45280</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>45175</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>45009</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>44792</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>45183</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>46247</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>46163</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>46290</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>46288</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>46246</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>46248</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>46248</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44608</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44919</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>44795</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>44991</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>45609</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45189</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>45659</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>45224</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>45406</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44950</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>45102</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>45600</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>44985</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>44899</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45627</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45246</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45019</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45631</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>44785</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45168</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45602</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45602</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45615</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45615</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45609</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>45790</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>44642</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44559</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>45638</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45393</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45393</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>45250</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45756</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45964</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>46135</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>46150</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>

--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45447</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>45057</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45742</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45607</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45009</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45456</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>44648</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45884</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45043</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45638</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44881</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>44694</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46257</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45394</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46000</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45440</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45897</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45587</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45056</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45450</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46084</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>46230</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44608</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45404</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>45513</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>46094</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>45975</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>46010</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>46013</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45611</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>45659</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>46167</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>46185</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>46203</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>46090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45252</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44608</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44665</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45590</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44603</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45756</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>46070</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>44774</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>44831</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>44818</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45260</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>44831</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>44864</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44504</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>44551</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44620</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>44770</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>44608</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>44826</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44862</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>44524</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44620</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44620</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44524</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44774</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44484</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45247</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45678</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45069</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45190</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44806</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45393</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45394</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45394</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>45450</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45407</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44784</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>45481</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45467</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>45484</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>45446</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44949</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44866</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45567</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>45512</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45539</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45447</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45506</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44494</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45476</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45887</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45548</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45889</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45614</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45436</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45800</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>46041</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>46044</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45897</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45429</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>45469</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45908</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>46056</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45348</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>46055</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>46055</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>46057</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>46057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>46057</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45915</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45915</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45916</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45919</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45251</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>46065</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45568</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45195</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>45929</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>45929</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45929</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45399</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45630</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>46084</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44914</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45938</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45938</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45587</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45568</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45943</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>44756</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>45945</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45946</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45236</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>45737</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45187</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45810</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>44673</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45712</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45953</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45953</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45351</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44998</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45964</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45614</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45813</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45813</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45076</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>45813</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>46132</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>46132</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>46132</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45978</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>46132</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45975</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45978</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>45679</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45979</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45982</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45232</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45982</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45986</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45600</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45128</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45988</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45988</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45630</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45989</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45988</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45989</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45993</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45072</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>46001</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46001</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>46002</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>46001</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46001</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>46008</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>46008</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>44978</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45749</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46007</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>44916</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44827</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45582</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44788</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45649</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45568</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45825</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>46023</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45257</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>46142</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45141</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>46010</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>44536</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>46142</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45919</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45280</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45537</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>46142</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44475</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45831</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44911</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>46153</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45614</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45737</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>46153</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45834</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45838</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>44602</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45345</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45351</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>44919</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45846</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45846</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>46164</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>46167</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>46167</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>46167</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>46167</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>46167</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         <v>44887</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45117</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>45601</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>46171</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>46171</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>46171</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>46171</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45800</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44557</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45513</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>46175</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45469</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>46175</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>46174</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>45602</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45812</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>46174</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>46177</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>46010</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>46177</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45537</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>46176</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44977</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>46181</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>46181</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>46181</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>46183</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45758</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>46185</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46185</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45602</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>46185</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>46188</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>45874</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>46191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45874</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>45418</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45642</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45875</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>46195</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>46197</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>46197</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45189</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>46198</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45882</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45471</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>46202</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45882</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>46202</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>46202</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>46202</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>46203</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45190</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>46205</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>46205</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>46205</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>46205</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>46205</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>46205</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>46205</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45345</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45609</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45610</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45587</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45090</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45429</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>46008</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45198</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>46254</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>46255</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45190</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>46212</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>46254</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>46254</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>46254</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45721</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45260</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>46254</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>46259</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45511</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45181</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>45145</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>44701</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>46190</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45307</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>44722</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45307</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>46264</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>45756</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45247</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>46266</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>46267</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45183</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45362</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>46224</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>46225</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45755</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45139</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45293</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>46270</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>45259</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>46239</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>46269</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45881</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45450</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45451</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>46248</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
         <v>45436</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>46274</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45251</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>46230</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46230</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>46275</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>46275</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45348</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45348</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>46275</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45345</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>46275</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45693</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45141</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>46279</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>45099</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>46281</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>46238</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>46281</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45536</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>46286</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45280</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>45175</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>45009</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>44792</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>45183</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>46247</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>46163</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>46290</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>46288</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>46246</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>46248</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>46248</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44608</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44919</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>44795</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>44991</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>45609</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45189</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>45659</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>45224</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>45406</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44950</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>45102</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>45600</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>44985</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>44899</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45627</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45246</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45019</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45631</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>44785</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45168</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45602</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45602</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45615</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45615</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45609</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>45790</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>44642</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44559</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>45638</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45393</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45393</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>45250</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45756</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45964</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>46135</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>46150</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>

--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45447</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>45057</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45742</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45607</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45456</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>45009</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45043</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45884</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45638</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44694</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46257</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45394</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46000</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45958</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45587</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45873</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45056</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>46205</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45832</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45440</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46230</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>46084</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44608</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>46013</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>46010</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45404</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45975</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45252</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>45611</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>45659</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>46167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>46185</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>46203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>46090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44665</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45513</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44608</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45590</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44603</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45756</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>46070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44524</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44831</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>44818</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>44774</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>45260</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44831</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44864</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44504</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44608</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>44551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44620</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44770</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44608</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44580</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>44826</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44862</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>44620</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>44620</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44524</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>44524</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44774</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>44490</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>44484</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45469</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45601</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45471</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44914</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45117</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45536</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45195</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44827</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>46001</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45345</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>46002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>45887</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45247</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>46007</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45790</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45615</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45481</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45889</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>45889</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45889</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45889</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>45189</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>45897</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45145</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45257</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45484</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>46041</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45908</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45446</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>45399</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45915</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45567</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>46044</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45916</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45418</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45469</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45800</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45919</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45251</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45511</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>46055</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45128</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44919</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>46055</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45568</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>46057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>46057</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>46056</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>45929</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>46057</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45929</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45929</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45929</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>44475</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>44795</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>46065</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45938</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45938</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>45187</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44536</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>45943</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45946</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45345</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45810</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>44949</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>45953</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>46084</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45251</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45953</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45813</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45813</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45813</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45587</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45602</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45964</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>44950</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45609</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45602</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45602</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44776</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45198</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>45631</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45975</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>45979</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45978</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45630</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45978</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45362</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45679</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45982</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45982</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45436</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45600</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45989</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45989</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45825</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45988</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45988</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45993</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45467</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>46001</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>46001</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>46001</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45831</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>46132</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>46132</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>46132</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45678</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>46132</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45190</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>45069</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45834</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45393</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45394</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45394</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45345</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45838</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45846</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45846</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45407</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>44919</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44701</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>44978</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>44991</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45102</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45348</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45181</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45019</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45919</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45099</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>44998</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45582</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>44722</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45450</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45451</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45800</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44784</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45649</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45721</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>46010</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>46023</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45609</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>46142</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>46142</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>46142</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44785</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45537</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45175</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45627</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45737</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>46153</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>46153</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45874</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45232</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45875</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44756</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>45758</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44602</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45568</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45548</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45874</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45537</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>45183</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>44911</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45351</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>46167</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>46164</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45307</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>46167</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>46167</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45659</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44899</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>46167</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>46167</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>46171</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>46171</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45882</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45259</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>46171</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>46171</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>46174</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>46174</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>45812</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>46176</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45882</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>46175</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>46175</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>46177</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>46177</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>46010</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>46181</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>46181</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45280</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>46181</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45610</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46183</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>46185</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>46185</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>46188</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45190</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45615</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45568</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>46191</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45183</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>46195</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>46197</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>45737</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>46197</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>46198</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45280</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>46202</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>46202</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>44792</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>46202</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>46205</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>46205</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>46203</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>46205</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>46205</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45476</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45260</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44673</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>46008</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>46212</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45602</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>46259</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45630</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45614</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>46190</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45429</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45756</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>46224</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>46264</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46266</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>46267</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>46225</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45513</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>46269</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>45881</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>46270</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45506</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>45247</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>46230</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>46230</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45293</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45236</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>46274</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>46275</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>46275</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>46275</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>46275</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>46279</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>44806</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>45447</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>46281</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>46281</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>45141</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>45141</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46238</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45614</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>44788</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45348</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45348</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>45009</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44887</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45307</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45587</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>44985</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45450</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46286</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45351</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>46246</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>46289</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>44494</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>44608</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46290</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>46163</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45190</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>46248</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>46247</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45406</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>46248</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>44977</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>46294</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46294</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46295</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46294</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46294</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45915</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>46248</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45090</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45693</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46254</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>46254</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>46205</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>46288</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45642</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46255</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>46254</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>46239</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45189</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>46205</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46254</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44911</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>46254</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45224</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45512</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45539</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44557</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>44916</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45429</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45076</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>45072</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45139</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>44866</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45609</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45436</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45168</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45600</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45712</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45749</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>45638</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45393</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45393</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44642</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>44559</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45250</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45756</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45964</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>46135</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46150</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>46294</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>

--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45447</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>45057</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45742</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45607</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45456</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>45009</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45043</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45884</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45638</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44694</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46257</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45394</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46000</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45958</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45587</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45873</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45056</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>46205</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45832</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45440</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46230</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>46084</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44608</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>46013</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>46010</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45404</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45975</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45252</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>45611</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>45659</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>46167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>46185</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>46203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>46090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44665</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45513</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44608</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45590</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44603</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45756</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>46070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44524</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44831</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>44818</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>44774</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>45260</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44831</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44864</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44504</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44608</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>44551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44620</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44770</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44608</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44580</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>44826</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44862</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>44620</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>44620</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44524</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>44524</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44774</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>44490</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>44484</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45469</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45601</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45471</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44914</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45117</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45536</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45195</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44827</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>46001</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45345</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>46002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>45887</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45247</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>46007</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45790</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45615</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45481</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45889</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>45889</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45889</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45889</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>45189</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>45897</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45145</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45257</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45484</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>46041</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45908</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45446</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>45399</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45915</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45567</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>46044</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45916</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45418</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45469</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45800</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45919</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45251</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45511</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>46055</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45128</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44919</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>46055</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45568</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>46057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>46057</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>46056</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>45929</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>46057</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45929</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45929</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45929</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>44475</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>44795</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>46065</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45938</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45938</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>45187</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44536</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>45943</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45946</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45345</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45810</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>44949</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>45953</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>46084</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45251</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45953</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45813</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45813</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45813</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45587</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45602</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45964</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>44950</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45609</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45602</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45602</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44776</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45198</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>45631</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45975</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>45979</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45978</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45630</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45978</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45362</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45679</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45982</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45982</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45436</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45600</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45989</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45989</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45825</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45988</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45988</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45993</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45467</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>46001</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>46001</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>46001</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45831</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>46132</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>46132</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>46132</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45678</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>46132</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45190</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>45069</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45834</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45393</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45394</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45394</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45345</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45838</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45846</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45846</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45407</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>44919</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44701</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>44978</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>44991</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45102</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45348</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45181</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45019</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45919</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45099</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>44998</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45582</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>44722</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45450</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45451</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45800</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44784</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45649</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45721</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>46010</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>46023</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45609</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>46142</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>46142</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>46142</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44785</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45537</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45175</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45627</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45737</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>46153</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>46153</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45874</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45232</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45875</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44756</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>45758</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44602</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45568</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45548</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45874</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45537</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>45183</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>44911</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45351</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>46167</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>46164</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45307</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>46167</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>46167</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45659</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44899</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>46167</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>46167</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>46171</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>46171</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45882</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45259</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>46171</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>46171</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>46174</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>46174</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>45812</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>46176</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45882</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>46175</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>46175</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>46177</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>46177</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>46010</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>46181</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>46181</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45280</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>46181</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45610</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46183</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>46185</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>46185</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>46188</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45190</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45615</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45568</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>46191</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45183</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>46195</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>46197</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>45737</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>46197</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>46198</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45280</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>46202</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>46202</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>44792</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>46202</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>46205</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>46205</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>46203</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>46205</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>46205</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45476</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45260</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44673</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>46008</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>46212</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45602</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>46259</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45630</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45614</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>46190</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45429</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45756</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>46224</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>46264</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46266</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>46267</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>46225</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45513</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>46269</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>45881</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>46270</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45506</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>45247</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>46230</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>46230</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45293</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45236</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>46274</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>46275</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>46275</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>46275</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>46275</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>46279</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>44806</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>45447</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>46281</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>46281</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>45141</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>45141</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46238</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45614</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>44788</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45348</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45348</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>45009</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44887</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45307</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45587</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>44985</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45450</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46286</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45351</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>46246</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>46289</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>44494</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>44608</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46290</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>46163</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45190</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>46248</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>46247</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45406</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>46248</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>44977</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>46294</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46294</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46295</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46294</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46294</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45915</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>46248</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45090</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45693</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46254</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>46254</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>46205</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>46288</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45642</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46255</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>46254</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>46239</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45189</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>46205</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46254</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44911</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>46254</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45224</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45512</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45539</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44557</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>44916</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45429</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45076</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>45072</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45139</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>44866</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45609</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45436</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45168</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45600</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45712</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45749</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>45638</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45393</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45393</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44642</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>44559</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45250</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45756</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45964</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>46135</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46150</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>46294</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>

--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45447</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45742</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45607</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45456</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>45009</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>44648</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45043</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45884</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45638</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44694</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46257</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45394</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46000</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46301</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>46301</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>45734</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45440</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45897</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45056</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>45587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>45873</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45958</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>46205</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>45832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>46230</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>46084</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>44608</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44665</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>45590</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>45404</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45513</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45252</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>45975</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>46010</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46013</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45611</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45659</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>46167</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>46185</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>46203</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>46090</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>46304</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44603</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45756</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>46070</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44524</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44746</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44774</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44831</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44818</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>45260</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44831</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44864</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44504</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>44608</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>44862</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44551</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44620</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>44620</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44524</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>44620</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44770</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44524</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44774</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44826</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44608</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44580</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45189</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44484</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>45659</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44806</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45224</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45406</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>44911</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>44950</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45737</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45190</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45102</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>44985</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45345</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45247</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>44899</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45627</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45393</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45394</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45394</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45450</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45407</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44776</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44784</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45246</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45019</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44919</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45678</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45069</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45481</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>45467</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45631</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44785</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>45117</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>45446</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>45168</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>44949</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44866</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>45601</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45887</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45512</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45602</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45602</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45539</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45889</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44557</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45513</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>45447</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45506</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>45469</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>45897</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45602</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44494</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45476</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45548</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45614</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45436</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45537</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>45908</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>44977</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45609</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44911</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45429</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45915</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45916</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>45602</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45348</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45919</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45790</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45568</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45418</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>45642</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>45195</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45929</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45929</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45484</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>45399</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>45567</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>45630</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45189</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45471</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44914</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45800</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45587</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45190</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45568</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45251</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>44756</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>45345</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45938</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45610</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45587</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45236</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>45737</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45187</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45090</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45810</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44673</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>45943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45429</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45945</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45712</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45813</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45813</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45813</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45351</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>44998</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45721</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45260</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45825</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45511</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45181</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45076</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45953</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45953</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45145</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45834</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44701</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45964</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45838</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45679</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45307</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45232</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45600</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45128</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45846</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45846</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45630</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>44722</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45307</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45756</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45247</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45072</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45183</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45362</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45978</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45800</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45139</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45293</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45975</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45259</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45978</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45450</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45451</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45758</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45749</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>44916</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44827</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45874</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45436</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45874</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45979</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45875</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45251</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>44788</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45982</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45982</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45882</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45348</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45348</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45882</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45345</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45693</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45141</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45986</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45568</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45257</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45099</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45141</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45988</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44536</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45988</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45989</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45988</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45280</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45536</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45989</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45280</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45175</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45009</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46001</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>46132</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>46132</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>44792</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>46001</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>46132</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45183</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>46132</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>46002</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>46001</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>46001</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>46008</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>46008</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>46007</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>44608</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44978</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>46041</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45582</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>46044</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45649</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>44919</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44795</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>46023</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>44991</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45469</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>46142</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45609</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>46056</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>46055</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>46055</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>46057</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>46057</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>46057</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>46010</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>46142</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>45919</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>45537</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>46142</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46065</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>46153</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>46153</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>46084</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>44602</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45351</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>46164</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>46167</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>46167</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>46167</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>46167</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>46167</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>46171</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>46171</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>46171</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>46171</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>46175</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>46175</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>46174</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45812</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>46174</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>46177</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>46010</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46177</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>46176</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>46181</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>46181</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>46181</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>46183</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>46185</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>46185</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>46188</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>46191</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>46195</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>46197</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>46197</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>46198</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>46202</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>46202</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>46202</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>46202</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>46203</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>46205</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>46205</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>46205</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>46205</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>46008</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>46212</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>46190</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>46264</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>46266</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>46267</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>46224</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46270</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>46269</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45881</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>46274</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>46230</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46230</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>46275</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>46275</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>46275</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>46275</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>46279</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>46281</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>46238</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>46281</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>46286</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>46247</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>46163</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>46289</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>46290</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>46246</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>46294</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>46248</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>46294</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>46294</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>46294</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>46248</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>46295</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>46248</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>46254</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46254</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46254</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>46205</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>46254</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>46255</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>46254</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>46288</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>46239</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45915</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>46205</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>46302</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>46259</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>46302</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>46303</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>46303</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>46303</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>46303</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>46303</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>46304</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>46304</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>46303</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>46303</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>46303</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>46304</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>46304</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>44642</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44559</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>45638</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>45393</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45393</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45250</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45756</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>45964</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>46135</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>46150</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>46294</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>

--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45447</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45742</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45607</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45456</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>45009</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>44648</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45043</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45884</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45638</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44694</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46257</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45394</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46000</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46301</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>46301</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>45734</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45440</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45897</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45056</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>45587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>45873</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45958</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>46205</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>45832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>46230</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>46084</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>44608</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44665</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>45590</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>45404</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45513</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45252</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>45975</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>46010</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46013</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45611</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45659</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>46167</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>46185</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>46203</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>46090</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>46304</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44603</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45756</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>46070</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44524</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44746</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44774</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44831</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44818</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>45260</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44831</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44864</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44504</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>44608</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>44862</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44551</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44620</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>44620</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44524</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>44620</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44770</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44524</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44774</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44826</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44608</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44580</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45189</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44484</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>45659</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44806</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45224</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45406</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>44911</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>44950</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45737</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45190</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45102</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>44985</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45345</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45247</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>44899</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45627</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45393</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45394</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45394</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45450</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45407</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44776</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44784</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45246</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45019</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44919</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45678</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45069</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45481</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>45467</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45631</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44785</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>45117</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>45446</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>45168</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>44949</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44866</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>45601</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45887</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45512</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45602</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45602</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45539</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45889</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44557</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45513</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>45447</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45506</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>45469</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>45897</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45602</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44494</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45476</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45548</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45614</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45436</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45537</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>45908</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>44977</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45609</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44911</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45429</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45915</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45916</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>45602</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45348</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45919</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45790</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45568</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45418</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>45642</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>45195</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45929</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45929</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45484</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>45399</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>45567</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>45630</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45189</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45471</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44914</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45800</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45587</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45190</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45568</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45251</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>44756</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>45345</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45938</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45610</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45587</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45236</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>45737</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45187</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45090</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45810</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44673</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>45943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45429</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45945</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45712</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45813</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45813</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45813</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45351</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>44998</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45721</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45260</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45825</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45511</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45181</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45076</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45953</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45953</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45145</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45834</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44701</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45964</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45838</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45679</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45307</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45232</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45600</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45128</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45846</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45846</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45630</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>44722</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45307</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45756</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45247</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45072</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45183</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45362</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45978</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45800</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45139</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45293</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45975</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45259</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45978</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45450</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45451</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45758</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45749</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>44916</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44827</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45874</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45436</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45874</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45979</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45875</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45251</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>44788</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45982</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45982</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45882</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45348</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45348</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45882</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45345</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45693</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45141</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45986</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45568</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45257</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45099</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45141</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45988</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44536</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45988</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45989</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45988</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45280</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45536</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45989</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45280</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45175</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45009</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46001</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>46132</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>46132</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>44792</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>46001</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>46132</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45183</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>46132</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>46002</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>46001</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>46001</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>46008</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>46008</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>46007</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>44608</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44978</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>46041</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45582</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>46044</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45649</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>44919</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44795</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>46023</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>44991</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45469</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>46142</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45609</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>46056</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>46055</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>46055</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>46057</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>46057</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>46057</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>46010</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>46142</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>45919</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>45537</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>46142</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46065</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>46153</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>46153</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>46084</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>44602</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45351</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>46164</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>46167</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>46167</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>46167</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>46167</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>46167</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>46171</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>46171</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>46171</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>46171</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>46175</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>46175</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>46174</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45812</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>46174</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>46177</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>46010</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46177</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>46176</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>46181</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>46181</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>46181</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>46183</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>46185</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>46185</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>46188</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>46191</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>46195</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>46197</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>46197</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>46198</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>46202</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>46202</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>46202</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>46202</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>46203</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>46205</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>46205</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>46205</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>46205</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>46008</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>46212</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>46190</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>46264</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>46266</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>46267</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>46224</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46270</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>46269</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45881</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>46274</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>46230</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46230</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>46275</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>46275</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>46275</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>46275</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>46279</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>46281</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>46238</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>46281</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>46286</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>46247</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>46163</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>46289</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>46290</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>46246</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>46294</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>46248</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>46294</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>46294</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>46294</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>46248</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>46295</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>46248</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>46254</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46254</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46254</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>46205</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>46254</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>46255</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>46254</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>46288</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>46239</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45915</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>46205</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>46302</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>46259</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>46302</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>46303</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>46303</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>46303</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>46303</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>46303</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>46304</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>46304</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>46303</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>46303</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>46303</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>46304</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>46304</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>44642</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44559</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>45638</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>45393</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45393</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45250</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45756</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>45964</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>46135</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>46150</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>46294</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>

--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45447</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45607</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45742</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45456</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>45009</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45043</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45884</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45638</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44694</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46257</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45394</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46000</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46301</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>46301</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>45734</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45587</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45897</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>45056</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>45958</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45440</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>46205</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>46230</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>46084</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45873</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>44608</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>45611</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45252</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>45404</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45659</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45975</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>46167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>46013</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46010</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>46185</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>44665</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45513</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>46203</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>46090</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44608</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>45590</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>46304</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44603</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45756</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>46070</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44524</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44746</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44774</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44831</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44818</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>45260</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44831</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44864</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44504</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>44608</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44551</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44620</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44770</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44608</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44580</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44826</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44862</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44620</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44620</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44524</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44774</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44490</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45469</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45601</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>45471</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45117</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45536</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45195</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>44827</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45345</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45247</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45481</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>45615</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45189</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45145</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>45257</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45446</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>45399</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45511</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45418</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44919</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45128</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45568</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45187</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44536</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45345</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45251</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>44949</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45587</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45602</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>44950</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>45602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>45602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>45609</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>45198</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44776</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45630</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45631</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45362</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45679</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45436</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45600</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45882</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44795</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45887</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45467</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45889</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45889</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45897</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>45678</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>45190</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>45919</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45069</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>45649</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>45393</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45394</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45394</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>45908</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>46010</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>46023</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45345</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>46142</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>46142</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>46142</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45537</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>45919</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45407</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>44919</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45929</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45614</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44701</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45929</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>44991</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>46153</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>46153</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45938</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>45938</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45102</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45943</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45348</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45945</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>45181</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45019</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45946</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44998</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45953</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45953</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44722</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44602</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45450</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45451</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>44784</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45721</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45964</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45609</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>44785</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45351</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45175</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45975</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45979</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45627</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45737</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45978</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45978</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>46167</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>46164</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>46167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45232</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45982</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45982</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>46167</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45986</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>44756</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>46167</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>46167</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45568</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45989</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45548</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45988</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45989</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45988</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45988</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45993</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45537</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45183</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>46001</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45307</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46001</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>46001</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45659</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>44899</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>46001</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45755</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>46002</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>46171</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46171</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>46007</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>46008</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46008</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>46171</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>46171</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45259</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>46174</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>46174</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45246</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45280</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45610</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45812</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>46176</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>46175</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>46175</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>46041</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>46177</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45190</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>46177</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45615</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45568</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>46010</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>46044</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>46181</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>46181</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45469</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>46055</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45183</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>46055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>46057</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>46181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>46057</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>46056</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>46057</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45737</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45280</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>46065</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>46183</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>46185</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>46185</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>46188</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44792</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45476</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45260</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>46084</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44673</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>46191</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45602</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45630</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45614</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>46195</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>46197</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>46197</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>46198</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45429</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45756</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>46202</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46202</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>46202</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>45513</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>46202</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>46132</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45506</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>46132</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45247</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>46132</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45293</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>46205</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46205</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45236</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>46205</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46203</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>46205</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44806</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45447</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45141</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45141</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45614</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44788</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45348</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45348</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45009</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44887</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>46008</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45307</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>46212</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45587</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44985</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45450</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45351</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>46190</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>46224</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45881</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>46270</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44494</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>44608</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>46230</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>46230</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>46274</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45190</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>46275</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46275</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>46275</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>46275</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45406</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>46279</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44977</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>46281</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>46281</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45090</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45693</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>46238</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45642</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>45189</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44911</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45224</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45512</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45539</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>46286</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44557</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44916</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>46246</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45429</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>46289</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>46290</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45076</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>46163</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>46248</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>45072</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>46247</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>46248</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45139</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>46294</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>46294</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44866</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>46295</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45609</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>46294</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45436</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45168</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>46294</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45915</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>46248</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46254</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>46254</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>46205</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>46254</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>46239</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>46205</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>46254</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>46254</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45600</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31703,7 +31703,7 @@
         <v>45712</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45749</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>46255</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>46303</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>46303</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>46303</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>46303</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>46303</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>46303</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>46303</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>46302</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>46302</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>46303</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45790</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>46259</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>45484</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>46304</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>46304</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45567</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>46304</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>46304</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>46308</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>46308</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>46309</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45800</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>46309</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>46309</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45251</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>46309</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>46264</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>46266</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>46308</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>45810</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>46311</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45813</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>46310</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45813</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>45813</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>46267</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>46311</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>46311</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45825</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>46269</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>46310</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45831</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45834</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45838</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45846</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45846</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45800</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45874</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>45875</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45758</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>45874</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45882</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45638</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45393</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45393</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>44642</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>44559</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>45250</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>45756</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>45964</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>46135</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>46150</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>46294</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>

--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45447</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45607</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45742</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45456</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>45009</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45043</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45884</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45638</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44694</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46257</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45394</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46000</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46301</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>46301</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>45734</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45587</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45897</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>45056</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>45958</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45440</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>46205</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>46230</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>46084</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45873</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>44608</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>45611</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45252</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>45404</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45659</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45975</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>46167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>46013</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46010</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>46185</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>44665</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45513</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>46203</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>46090</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44608</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>45590</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>46304</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44603</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45756</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>46070</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44524</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44746</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44774</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44831</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44818</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>45260</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44831</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44864</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44504</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>44608</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44551</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44620</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44770</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44608</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44580</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44826</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44862</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44620</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44620</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44524</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44774</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44490</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45469</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45601</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>45471</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45117</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45536</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45195</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>44827</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45345</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45247</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45481</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>45615</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45189</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45145</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>45257</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45446</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>45399</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45511</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45418</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44919</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45128</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45568</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45187</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44536</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45345</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45251</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>44949</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45587</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45602</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>44950</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>45602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>45602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>45609</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>45198</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44776</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45630</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45631</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45362</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45679</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45436</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45600</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45882</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44795</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45887</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45467</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45889</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45889</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45897</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>45678</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>45190</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>45919</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45069</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>45649</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>45393</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45394</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45394</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>45908</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>46010</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>46023</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45345</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>46142</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>46142</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>46142</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45537</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>45919</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45407</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>44919</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45929</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45614</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44701</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45929</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>44991</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>46153</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>46153</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45938</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>45938</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45102</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45943</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45348</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45945</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>45181</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45019</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45946</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44998</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45953</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45953</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44722</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44602</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45450</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45451</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>44784</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45721</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45964</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45609</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>44785</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45351</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45175</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45975</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45979</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45627</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45737</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45978</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45978</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>46167</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>46164</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>46167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45232</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45982</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45982</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>46167</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45986</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>44756</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>46167</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>46167</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45568</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45989</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45548</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45988</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45989</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45988</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45988</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45993</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45537</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45183</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>46001</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45307</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46001</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>46001</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45659</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>44899</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>46001</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45755</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>46002</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>46171</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46171</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>46007</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>46008</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46008</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>46171</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>46171</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45259</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>46174</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>46174</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45246</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45280</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45610</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45812</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>46176</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>46175</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>46175</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>46041</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>46177</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45190</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>46177</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45615</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45568</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>46010</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>46044</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>46181</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>46181</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45469</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>46055</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45183</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>46055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>46057</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>46181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>46057</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>46056</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>46057</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45737</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45280</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>46065</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>46183</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>46185</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>46185</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>46188</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44792</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45476</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45260</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>46084</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44673</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>46191</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45602</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45630</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45614</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>46195</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>46197</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>46197</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>46198</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45429</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45756</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>46202</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46202</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>46202</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>45513</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>46202</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>46132</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45506</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>46132</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45247</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>46132</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45293</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>46205</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46205</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45236</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>46205</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46203</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>46205</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44806</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45447</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45141</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45141</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45614</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44788</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45348</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45348</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45009</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44887</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>46008</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45307</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>46212</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45587</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44985</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45450</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45351</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>46190</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>46224</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45881</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>46270</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44494</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>44608</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>46230</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>46230</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>46274</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45190</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>46275</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46275</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>46275</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>46275</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45406</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>46279</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44977</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>46281</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>46281</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45090</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45693</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>46238</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45642</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>45189</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44911</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45224</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45512</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45539</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>46286</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44557</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44916</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>46246</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45429</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>46289</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>46290</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45076</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>46163</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>46248</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>45072</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>46247</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>46248</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45139</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>46294</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>46294</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44866</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>46295</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45609</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>46294</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45436</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45168</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>46294</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45915</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>46248</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46254</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>46254</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>46205</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>46254</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>46239</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>46205</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>46254</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>46254</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45600</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31703,7 +31703,7 @@
         <v>45712</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45749</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>46255</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>46303</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>46303</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>46303</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>46303</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>46303</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>46303</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>46303</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>46302</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>46302</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>46303</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45790</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>46259</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>45484</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>46304</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>46304</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45567</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>46304</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>46304</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>46308</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>46308</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>46309</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45800</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>46309</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>46309</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45251</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>46309</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>46264</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>46266</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>46308</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>45810</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>46311</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45813</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>46310</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45813</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>45813</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>46267</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>46311</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>46311</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45825</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>46269</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>46310</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45831</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45834</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45838</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45846</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45846</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45800</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45874</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>45875</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45758</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>45874</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45882</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45638</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45393</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45393</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>44642</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>44559</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>45250</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>45756</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>45964</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>46135</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>46150</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>46294</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>

--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45467</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>45132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>45447</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>45057</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45607</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>45742</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45009</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45456</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44648</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>45912</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45884</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45043</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45638</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>46281</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>46257</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>44881</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>44694</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45394</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>46000</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>44588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>46301</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>46301</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45734</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45897</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45440</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>46205</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45832</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>46230</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45958</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>46084</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45873</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>45587</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45056</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>45450</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44608</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44608</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>45404</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>45659</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>46167</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>46185</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44665</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>45975</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>46203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>45590</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>44897</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>46090</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46010</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>46013</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>46304</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>45513</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>45611</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>45252</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>44603</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45756</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44746</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44774</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44831</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44818</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45260</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44831</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>44864</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44504</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44608</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44551</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44701</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44620</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44770</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44608</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>44580</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44826</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44862</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>44620</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>44620</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44524</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>44774</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45887</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45190</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>45889</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45889</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>45889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>45247</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>45889</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>44776</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>45897</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>45678</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45069</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45908</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45351</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>45915</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>46164</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>45916</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>46167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45919</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>46167</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>46167</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>46167</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>44806</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45929</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45929</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45929</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45929</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>46171</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>46171</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>46171</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>46171</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>44919</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>44795</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>45938</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45938</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>44991</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45609</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46175</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>46175</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45189</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45659</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45812</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>46174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>46177</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45943</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>46010</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45224</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45393</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45394</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45406</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>46177</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45945</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>45394</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>45450</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45407</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44950</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45946</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>44784</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>46176</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>46181</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45102</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>46181</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45600</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>46181</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>46183</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44985</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45953</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45953</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44899</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45627</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>46185</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>46185</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45246</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45019</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45964</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>46188</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45481</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>46191</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45631</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>44785</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>46195</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>46197</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>46197</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45978</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>46198</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>45975</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45168</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45978</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>46202</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>46202</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>46202</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>46202</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45979</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>46203</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45982</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45982</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45602</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45602</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>46205</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>46205</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>45986</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>46205</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45988</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45988</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45989</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45615</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45988</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>46008</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45989</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>46212</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45993</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45446</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45615</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>46190</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45609</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>46001</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>46001</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>46002</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>46001</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46001</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>46224</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45881</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>46008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>46008</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>46230</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46230</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46007</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>44949</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>46279</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>46281</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45790</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>46238</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44866</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>46281</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>46286</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45484</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45567</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>46041</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>46044</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>45800</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45469</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>46247</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>46163</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>46289</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>45251</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>46290</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>46246</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>46056</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>46055</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>46055</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>46057</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>46057</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>46057</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45512</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>46294</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45810</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>46248</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45813</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45813</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>45813</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>46294</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>46294</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>46065</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>46294</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>46248</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45825</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>46295</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>45831</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>46084</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>45539</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>45834</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>46248</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45838</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>46254</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>46254</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>46254</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>46205</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>46254</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>46255</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>46254</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45447</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>45506</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>46239</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45915</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45846</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>46205</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45846</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>44494</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45476</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>46302</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45548</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>46259</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>46302</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>46303</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45800</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>46303</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>46303</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>46303</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>46303</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>46304</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>46304</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>46303</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45614</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>46303</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>46303</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>46304</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45758</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>46304</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45436</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>45874</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>45874</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45875</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46132</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>46132</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46132</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>46132</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>46308</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45882</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45882</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44911</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45429</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>46308</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>46308</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>46264</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45348</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>46267</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>46310</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>46309</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>46309</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>46310</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46309</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>46266</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>46309</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46269</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>46311</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>46270</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45568</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>46311</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44978</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46311</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45582</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45195</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45649</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45399</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45630</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46274</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46023</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46142</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44914</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>46317</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>46275</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>46317</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>46010</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>46317</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>46142</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>45919</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>46275</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45587</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>46317</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>46275</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>46275</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45537</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>46142</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45568</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44756</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>46153</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45236</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45737</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45187</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>46153</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>44673</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>45712</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45351</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44602</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44998</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45614</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>45076</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>45679</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45232</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>45600</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>45128</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45630</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45072</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>45749</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44916</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44827</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44788</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45568</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45257</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45141</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44536</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45280</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>44911</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45614</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45737</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45345</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44919</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44887</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45117</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45601</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44557</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>45513</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45469</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45602</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45537</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>44977</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45602</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>45418</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45642</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45189</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45471</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45190</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45345</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45609</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45610</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45587</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45090</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45429</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45198</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>45190</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45721</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45260</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45511</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45181</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45145</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>44701</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>45307</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>44722</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>45307</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>45756</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45247</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>45183</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>45362</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>45755</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>45139</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45293</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45259</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45450</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45451</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>45436</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45251</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45348</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45348</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45345</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45693</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45141</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45099</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45536</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>45280</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45175</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44792</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45183</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>44642</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>44559</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45638</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>45393</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45393</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45250</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45756</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>45964</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>46135</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>46150</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>46294</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>

--- a/Översikt BJURHOLM.xlsx
+++ b/Översikt BJURHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45884</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45519</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44691</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45467</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>45132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>45447</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>45057</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45607</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>45742</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45009</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45456</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44648</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>45912</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45884</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45043</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45638</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>46281</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>46257</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>44881</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>44694</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45394</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>46000</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>44588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>46301</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>46301</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45734</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45897</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45440</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>46205</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45832</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>46230</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45958</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>46084</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45873</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>45587</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45056</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>45450</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44608</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44608</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>45404</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>45659</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>46167</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>46185</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44665</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>45975</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>46203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>45590</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>44897</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>46090</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46010</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>46013</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>46304</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>45513</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>45611</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>45252</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>44603</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45756</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44746</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44774</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44831</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44818</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45260</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44831</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>44864</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44504</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44608</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44551</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44701</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44620</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44770</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44608</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>44580</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44826</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44862</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>44620</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>44620</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44524</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>44774</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45887</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45190</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>45889</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45889</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>45889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>45247</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>45889</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>44776</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>45897</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>45678</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45069</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45908</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45351</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>45915</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>46164</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>45916</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>46167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45919</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>46167</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>46167</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>46167</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>44806</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45929</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45929</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45929</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45929</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>46171</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>46171</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>46171</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>46171</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>44919</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>44795</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>45938</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45938</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>44991</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45609</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46175</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>46175</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45189</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45659</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45812</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>46174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>46177</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45943</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>46010</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45224</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45393</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45394</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45406</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>46177</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45945</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>45394</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>45450</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45407</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44950</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45946</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>44784</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>46176</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>46181</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45102</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>46181</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45600</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>46181</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>46183</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44985</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45953</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45953</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44899</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45627</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>46185</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>46185</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45246</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45019</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45964</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>46188</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45481</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>46191</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45631</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>44785</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>46195</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>46197</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>46197</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45978</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>46198</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>45975</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45168</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45978</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>46202</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>46202</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>46202</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>46202</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45979</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>46203</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45982</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45982</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45602</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45602</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>46205</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>46205</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>45986</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>46205</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45988</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45988</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45989</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45615</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45988</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>46008</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45989</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>46212</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45993</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45446</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45615</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>46190</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45609</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>46001</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>46001</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>46002</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>46001</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46001</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>46224</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45881</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>46008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>46008</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>46230</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46230</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46007</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>44949</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>46279</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>46281</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45790</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>46238</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44866</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>46281</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>46286</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45484</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45567</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>46041</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>46044</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>45800</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45469</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>46247</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>46163</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>46289</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>45251</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>46290</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>46246</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>46056</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>46055</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>46055</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>46057</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>46057</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>46057</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45512</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>46294</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45810</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>46248</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45813</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45813</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>45813</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>46294</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>46294</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>46065</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>46294</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>46248</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45825</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>46295</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>45831</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>46084</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>45539</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>45834</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>46248</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45838</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>46254</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>46254</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>46254</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>46205</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>46254</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>46255</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>46254</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45447</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>45506</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>46239</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45915</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45846</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>46205</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45846</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>44494</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45476</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>46302</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45548</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>46259</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>46302</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>46303</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45800</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>46303</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>46303</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>46303</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>46303</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>46304</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>46304</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>46303</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45614</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>46303</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>46303</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>46304</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45758</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>46304</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45436</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>45874</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>45874</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45875</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46132</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>46132</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46132</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>46132</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>46308</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45882</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45882</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44911</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45429</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>46308</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>46308</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>46264</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45348</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>46267</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>46310</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>46309</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>46309</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>46310</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46309</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>46266</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>46309</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46269</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>46311</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>46270</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45568</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>46311</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44978</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46311</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45582</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45195</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45649</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45399</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45630</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46274</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46023</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46142</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44914</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>46317</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>46275</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>46317</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>46010</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>46317</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>46142</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>45919</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>46275</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45587</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>46317</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>46275</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>46275</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45537</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>46142</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45568</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44756</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>46153</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45236</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45737</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45187</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>46153</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>44673</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>45712</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45351</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44602</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44998</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45614</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>45076</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>45679</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45232</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>45600</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>45128</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45630</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45072</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>45749</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44916</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44827</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44788</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45568</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45257</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45141</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44536</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45280</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>44911</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45614</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45737</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45345</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44919</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44887</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45117</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45601</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44557</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>45513</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45469</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45602</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45537</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>44977</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45602</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>45418</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45642</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45189</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45471</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45190</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45345</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45609</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45610</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45587</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45090</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45429</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45198</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>45190</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45721</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45260</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45511</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45181</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45145</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>44701</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>45307</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>44722</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>45307</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>45756</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45247</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>45183</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>45362</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>45755</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>45139</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45293</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45259</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45450</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45451</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>45436</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45251</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45348</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45348</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45345</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45693</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45141</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45099</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45536</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>45280</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45175</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44792</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45183</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>44642</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>44559</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45638</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>45393</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45393</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45250</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45756</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>45964</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>46135</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>46150</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>46294</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
